--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JNVST Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JNVST Questions'!$A$1:$U$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,18 +28,9 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001D4ED8"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,16 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,30 +426,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,80 +481,85 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Fixed Question</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Question English</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Question Assamese</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -607,61 +593,65 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Find the place value of 5 in 5,432.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -672,156 +662,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>JNVST Question Bank — Bulk Upload Instructions</t>
+          <t>JNVST Question Bulk Upload Instructions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>This template is ONLY for the JNVST Course Question Bank.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subject Name must exactly match an existing JNVST Subject.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>School Course questions are not changed by this upload.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lesson Code must match an existing JNVST Lesson/Sub-lesson under that subject.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Subject Name must exactly match an existing JNVST Subject.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Medium must be COMMON for MAT questions, or ENGLISH / ASSAMESE for language-specific questions.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Lesson Code must match an existing Lesson/Sub-lesson under that Subject.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Variation Group: use the same code for similar questions with small variations. The assignment generator selects at most one question from a variation group.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Medium must be ENGLISH, ASSAMESE or BOTH.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fixed Question: YES or NO. This is bank metadata; teachers can also select fixed questions directly while generating an assignment.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Use the same Variation Group for similar questions with small variations.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Question Type / Marks / Cognitive Level / Difficulty are included for template compatibility. The current JNVST mock bank stores the core question and assignment metadata shown above.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>The JNVST assignment generator selects at most one question from a Variation Group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Question Type must be MCQ, Short or Long.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>For MCQ, Correct Answer must be A, B, C or D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Topic is the teacher-defined topic within the selected Lesson/Sub-lesson.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Existing questions with the same teacher, JNVST subject, lesson and exact English/Assamese text are skipped as duplicates.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>This upload writes to public.mock_question_bank only. It does not create or modify School Course questions.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -583,14 +583,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Place Value</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NUM-001</t>
-        </is>
-      </c>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -616,28 +612,28 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Find the place value of 5 in 5,432.</t>
+          <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>\frac{5}{4}</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>\frac{7}{4}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>\frac{9}{4}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>\frac{11}{4}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -649,7 +645,11 @@
           <t>A</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Convert to a common denominator: \frac{1}{2}=\frac{2}{4}.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -662,65 +662,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>JNVST Question Bulk Upload Instructions</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Subject Name must exactly match an existing JNVST Subject.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lesson Code must match an existing JNVST Lesson/Sub-lesson under that subject.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Medium must be COMMON for MAT questions, or ENGLISH / ASSAMESE for language-specific questions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Variation Group: use the same code for similar questions with small variations. The assignment generator selects at most one question from a variation group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fixed Question: YES or NO. This is bank metadata; teachers can also select fixed questions directly while generating an assignment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Question Type / Marks / Cognitive Level / Difficulty are included for template compatibility. The current JNVST mock bank stores the core question and assignment metadata shown above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>This upload writes to public.mock_question_bank only. It does not create or modify School Course questions.</t>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mathematics is supported directly inside Excel cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Enter LaTeX-style expressions such as \frac{3}{4}, x^2, \sqrt{16}, \times and \div in Question, Option A-D, and Explanation cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>The system converts these expressions to properly rendered mathematics when the question is displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>You may also use explicit math delimiters \( ... \) or \[ ... \] if preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Do not use Excel floating Equation objects; enter the equation as text in the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>For diagrams, use the question image/PDF upload workflow where applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Subject Name and Lesson Code must match existing JNVST records.</t>
         </is>
       </c>
     </row>

--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JNVST Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JNVST Questions'!$A$1:$AD$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -30,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +65,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,31 +433,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,109 +472,145 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Lesson Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Variation Group</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fixed Question</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Local Passage No.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Question Order</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Passage Title English</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Passage English</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Passage Title Assamese</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Passage Assamese</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Question English</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Question Assamese</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -573,85 +620,200 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>ARITHMETIC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>ENGLISH</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Fractions</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
+          <t>FRA-ADD-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>\frac{5}{4}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>\frac{7}{4}</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>\frac{9}{4}</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>\frac{11}{4}</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Convert to a common denominator: \frac{1}{2}=\frac{2}{4}.</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Convert to a common denominator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ARITHMETIC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ENGLISH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FRA-ADD-001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Find the value of \frac{1}{4}+\frac{3}{4}.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>\frac{3}{4}</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>\frac{5}{4}</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AD3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -662,75 +824,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="n"/>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>JNVST Question Bank — Variation Group Bulk Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Variation Group is optional. Give the same group code to similar alternative questions, e.g. FRA-ADD-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>When the Variation Group Rule is enabled in Question Paper Generator, at most ONE question from each non-empty group is selected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>If two mandatory questions have the same Variation Group, paper generation stops and asks you to keep only one mandatory question from that group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Questions without a Variation Group are unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fixed Question and Variation Group are independent: Fixed marks a question as preferred/mandatory; Variation Group controls alternative selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>This upload writes to mock_question_bank only. School Course Question Bank is not modified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Part: EVS_MCQ, EVS_PASSAGE, LANGUAGE_PASSAGE, ARITHMETIC, or the appropriate MAT part.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JNVST Question Bulk Upload Instructions</t>
+          <t>Passage questions must still use one Local Passage No. and Question Order 1–5.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mathematics is supported directly inside Excel cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Enter LaTeX-style expressions such as \frac{3}{4}, x^2, \sqrt{16}, \times and \div in Question, Option A-D, and Explanation cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>The system converts these expressions to properly rendered mathematics when the question is displayed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>You may also use explicit math delimiters \( ... \) or \[ ... \] if preferred.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Do not use Excel floating Equation objects; enter the equation as text in the cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>For diagrams, use the question image/PDF upload workflow where applicable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Subject Name and Lesson Code must match existing JNVST records.</t>
+          <t>LaTeX-style mathematics such as \frac{3}{4}, x^2, \sqrt{16}, \times and \div is supported.</t>
         </is>
       </c>
     </row>

--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JNVST Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JNVST Questions'!$A$1:$AD$3</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -32,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,9 +58,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,35 +426,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="45" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,145 +461,109 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Part</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Lesson Code</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Lesson Code</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Variation Group</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Variation Group</t>
+          <t>Fixed Question</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Fixed Question</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Question Type</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Cognitive Level</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Cognitive Level</t>
+          <t>Difficulty</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question English</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Local Passage No.</t>
+          <t>Question Assamese</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Question Order</t>
+          <t>Option A English</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Passage Title English</t>
+          <t>Option B English</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Passage English</t>
+          <t>Option C English</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Passage Title Assamese</t>
+          <t>Option D English</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Passage Assamese</t>
+          <t>Option A Assamese</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Question English</t>
+          <t>Option B Assamese</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Question Assamese</t>
+          <t>Option C Assamese</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Option A English</t>
+          <t>Option D Assamese</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Option B English</t>
+          <t>Correct Answer</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Option C English</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Option D English</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Option A Assamese</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Option B Assamese</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Option C Assamese</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Option D Assamese</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -620,200 +573,85 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARITHMETIC</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ENGLISH</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Fractions</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FRA-ADD-001</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>\frac{5}{4}</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>\frac{7}{4}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>\frac{9}{4}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\frac{11}{4}</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>\frac{5}{4}</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>\frac{7}{4}</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>\frac{9}{4}</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>\frac{11}{4}</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Convert to a common denominator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arithmetic</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ARITHMETIC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ENGLISH</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fractions</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FRA-ADD-001</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Find the value of \frac{1}{4}+\frac{3}{4}.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>\frac{3}{4}</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>\frac{5}{4}</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+          <t>Convert to a common denominator: \frac{1}{2}=\frac{2}{4}.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -824,79 +662,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>JNVST Question Bank — Variation Group Bulk Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Variation Group is optional. Give the same group code to similar alternative questions, e.g. FRA-ADD-001.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>When the Variation Group Rule is enabled in Question Paper Generator, at most ONE question from each non-empty group is selected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>If two mandatory questions have the same Variation Group, paper generation stops and asks you to keep only one mandatory question from that group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Questions without a Variation Group are unaffected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fixed Question and Variation Group are independent: Fixed marks a question as preferred/mandatory; Variation Group controls alternative selection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>This upload writes to mock_question_bank only. School Course Question Bank is not modified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Part: EVS_MCQ, EVS_PASSAGE, LANGUAGE_PASSAGE, ARITHMETIC, or the appropriate MAT part.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="2" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Passage questions must still use one Local Passage No. and Question Order 1–5.</t>
+          <t>JNVST Question Bulk Upload Instructions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LaTeX-style mathematics such as \frac{3}{4}, x^2, \sqrt{16}, \times and \div is supported.</t>
+          <t>Mathematics is supported directly inside Excel cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Enter LaTeX-style expressions such as \frac{3}{4}, x^2, \sqrt{16}, \times and \div in Question, Option A-D, and Explanation cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>The system converts these expressions to properly rendered mathematics when the question is displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>You may also use explicit math delimiters \( ... \) or \[ ... \] if preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Do not use Excel floating Equation objects; enter the equation as text in the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>For diagrams, use the question image/PDF upload workflow where applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Subject Name and Lesson Code must match existing JNVST records.</t>
         </is>
       </c>
     </row>

--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -486,80 +486,85 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Question English</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Question Assamese</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -586,7 +591,6 @@
           <t>Fractions</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -594,58 +598,58 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>\frac{5}{4}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>\frac{7}{4}</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>\frac{9}{4}</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>\frac{11}{4}</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Convert to a common denominator: \frac{1}{2}=\frac{2}{4}.</t>
         </is>
@@ -662,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -671,13 +675,6 @@
     <row r="1">
       <c r="A1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -731,6 +728,13 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>Subject Name and Lesson Code must match existing JNVST records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Common: write YES for questions frequently asked in exams (any Difficulty level); NO or blank otherwise. Questions in the same Variation Group as a Common question are treated as Common automatically.</t>
         </is>
       </c>
     </row>

--- a/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
+++ b/JNVST_Question_Bank_Bulk_Upload_Template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,8 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,6 +569,11 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Explanation Assamese</t>
         </is>
       </c>
     </row>
@@ -666,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -738,6 +745,13 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Explanation Assamese (optional): leave it blank and the English Explanation is translated into Assamese automatically for Assamese and Common (MAT) questions. You can check and correct it later in the Question Bank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
